--- a/storage/programas/3/evidencias/elemento_1/actividad_1_1/template_evidencia_actividad_34_registro__seguridad.xlsx
+++ b/storage/programas/3/evidencias/elemento_1/actividad_1_1/template_evidencia_actividad_34_registro__seguridad.xlsx
@@ -4,15 +4,243 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Registro +Seguridad" state="visible" r:id="rId3"/>
+    <sheet sheetId="1" name="Registro +Seguridad" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="74">
+  <si>
+    <t xml:space="preserve">PROGRAMA DE GESTIÓN OIEM CONTRATISTAS
+SEGURIDAD CONTRATISTA</t>
+  </si>
+  <si>
+    <t>Nombre EECC</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Repositorio Documental</t>
+  </si>
+  <si>
+    <t>Dependencia</t>
+  </si>
+  <si>
+    <t>TEAMS - EVIDENCIA DE ACTIVIDADES</t>
+  </si>
+  <si>
+    <t>Mes Informado</t>
+  </si>
+  <si>
+    <t>N° personas nuevas</t>
+  </si>
+  <si>
+    <t>Ítem</t>
+  </si>
+  <si>
+    <t>Actividades de Programa</t>
+  </si>
+  <si>
+    <t>Descripción y criterios</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Frecuencia</t>
+  </si>
+  <si>
+    <t>Evidencia</t>
+  </si>
+  <si>
+    <t>Cumplimiento</t>
+  </si>
+  <si>
+    <t>Ene</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Abr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Ago</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dic</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ELEMENTO 1: Liderazgo y compromiso</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Ejecución del Programa SAFEALIGN</t>
+  </si>
+  <si>
+    <t>Mensual</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Participación en CPHS de faena</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Reunión de accountability</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>ELEMENTO 2: Evaluación del riesgo</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Análisis de riesgos cualitativo (AST)</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ELEMENTO 5: Competencias y capacitación</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Ejecución de inducciones</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Cumplimiento plan capacitación anual</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>ELEMENTO 6-7: Operaciones e Integridad Mecánica</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Aplicación lista verificación OBS/INSP/MMC</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Gestión de cierre de tarjetas</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>ELEMENTO 9: Servicios de terceros</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Acreditación EECC y trabajadores</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Verificación laboral</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>Reunión accountability mensual</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>ELEMENTO 10: Investigación de accidentes</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>Envío informe investigación en plazo</t>
+  </si>
+  <si>
+    <t>Según ocurrencia</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Verificación cierre acciones correctivas</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>ELEMENTO 12: Evaluación y mejora</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>N° incidentes no registrables</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>N° incidentes registrables</t>
+  </si>
+  <si>
+    <t>TOTAL MENSUAL</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -20,16 +248,73 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="374151"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="6B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="003594"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003594"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="475569"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="E8F0FE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -37,12 +322,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,17 +695,1294 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A41:A81"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="9" max="9" width="3.6328125" customWidth="1"/>
-    <col min="10" max="10" width="1.453125" customWidth="1"/>
-    <col min="19" max="19" width="3.90625" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="41" ht="57.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="68.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="40" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="H3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S10" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S17" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S20" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S23" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S24" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S27" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="H31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="J3:S3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="J4:S4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="B9:S9"/>
+    <mergeCell ref="B13:S13"/>
+    <mergeCell ref="B15:S15"/>
+    <mergeCell ref="B18:S18"/>
+    <mergeCell ref="B21:S21"/>
+    <mergeCell ref="B25:S25"/>
+    <mergeCell ref="B28:S28"/>
+    <mergeCell ref="A31:C31"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
